--- a/РАБОЧИЙ СТОЛ/расчет Останкино СЫРЫ/дв 07,07,26 днрсч ост сыр.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет Останкино СЫРЫ/дв 07,07,26 днрсч ост сыр.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7DA0A8-CEAC-4C16-A26B-70247DF18D9B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6E2024-2750-45D6-AA2C-BCB51CB7323D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -250,6 +247,9 @@
   </si>
   <si>
     <t>Сыч/Прод Коровино Тильзитер Оригин 50% ВЕС НОВАЯ (5 кг брус) СЗМЖ  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>итого</t>
   </si>
 </sst>
 </file>
@@ -838,37 +838,37 @@
         <v>15</v>
       </c>
       <c r="R3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="V3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
@@ -907,34 +907,34 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
@@ -1062,10 +1062,10 @@
     </row>
     <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C6" s="1">
         <v>272.108</v>
@@ -1128,10 +1128,10 @@
         <v>4.0884</v>
       </c>
       <c r="AA6" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB6" s="1">
-        <f>G6*R6</f>
+        <f t="shared" ref="AB6:AB44" si="3">G6*R6</f>
         <v>0</v>
       </c>
       <c r="AC6" s="1"/>
@@ -1157,10 +1157,10 @@
     </row>
     <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C7" s="1">
         <v>87</v>
@@ -1190,16 +1190,16 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1">
-        <f t="shared" ref="Q7:Q44" si="3">E7/5</f>
+        <f t="shared" ref="Q7:Q44" si="4">E7/5</f>
         <v>0.6</v>
       </c>
       <c r="R7" s="5"/>
       <c r="S7" s="1">
-        <f t="shared" ref="S7:S44" si="4">(F7+O7+P7+R7)/Q7</f>
+        <f t="shared" ref="S7:S44" si="5">(F7+O7+P7+R7)/Q7</f>
         <v>140</v>
       </c>
       <c r="T7" s="1">
-        <f t="shared" ref="T7:T44" si="5">(F7+O7+P7)/Q7</f>
+        <f t="shared" ref="T7:T44" si="6">(F7+O7+P7)/Q7</f>
         <v>140</v>
       </c>
       <c r="U7" s="1">
@@ -1221,10 +1221,10 @@
         <v>2.4</v>
       </c>
       <c r="AA7" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB7" s="1">
-        <f>G7*R7</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC7" s="1"/>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1">
         <v>57</v>
@@ -1279,18 +1279,18 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R8" s="5"/>
       <c r="S8" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T8" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="T8" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="U8" s="1">
         <v>2</v>
       </c>
@@ -1310,10 +1310,10 @@
         <v>1.4</v>
       </c>
       <c r="AA8" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB8" s="1">
-        <f>G8*R8</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC8" s="1"/>
@@ -1339,10 +1339,10 @@
     </row>
     <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1">
         <v>142.892</v>
@@ -1372,18 +1372,18 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.3204</v>
       </c>
       <c r="R9" s="5"/>
       <c r="S9" s="1">
-        <f t="shared" si="4"/>
-        <v>103.21872159951529</v>
-      </c>
-      <c r="T9" s="1">
         <f t="shared" si="5"/>
         <v>103.21872159951529</v>
       </c>
+      <c r="T9" s="1">
+        <f t="shared" si="6"/>
+        <v>103.21872159951529</v>
+      </c>
       <c r="U9" s="1">
         <v>5.8715999999999999</v>
       </c>
@@ -1403,10 +1403,10 @@
         <v>0</v>
       </c>
       <c r="AA9" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB9" s="1">
-        <f>G9*R9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC9" s="1"/>
@@ -1432,10 +1432,10 @@
     </row>
     <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1">
         <v>145</v>
@@ -1463,18 +1463,18 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R10" s="5"/>
       <c r="S10" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T10" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="T10" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="U10" s="1">
         <v>0</v>
       </c>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AA10" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB10" s="1">
-        <f>G10*R10</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC10" s="1"/>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1">
         <v>420</v>
@@ -1562,18 +1562,18 @@
         <v>96</v>
       </c>
       <c r="Q11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.6</v>
       </c>
       <c r="R11" s="5"/>
       <c r="S11" s="1">
-        <f t="shared" si="4"/>
-        <v>216.53846153846152</v>
-      </c>
-      <c r="T11" s="1">
         <f t="shared" si="5"/>
         <v>216.53846153846152</v>
       </c>
+      <c r="T11" s="1">
+        <f t="shared" si="6"/>
+        <v>216.53846153846152</v>
+      </c>
       <c r="U11" s="1">
         <v>29.8</v>
       </c>
@@ -1593,10 +1593,10 @@
         <v>19.600000000000001</v>
       </c>
       <c r="AA11" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB11" s="1">
-        <f>G11*R11</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC11" s="1"/>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
         <v>436</v>
@@ -1657,18 +1657,18 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.4</v>
       </c>
       <c r="R12" s="5"/>
       <c r="S12" s="1">
-        <f t="shared" si="4"/>
-        <v>176.25</v>
-      </c>
-      <c r="T12" s="1">
         <f t="shared" si="5"/>
         <v>176.25</v>
       </c>
+      <c r="T12" s="1">
+        <f t="shared" si="6"/>
+        <v>176.25</v>
+      </c>
       <c r="U12" s="1">
         <v>8.4</v>
       </c>
@@ -1688,10 +1688,10 @@
         <v>5</v>
       </c>
       <c r="AA12" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB12" s="1">
-        <f>G12*R12</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC12" s="1"/>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1">
         <v>920</v>
@@ -1752,18 +1752,18 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="R13" s="5"/>
       <c r="S13" s="1">
-        <f t="shared" si="4"/>
-        <v>99.431818181818173</v>
-      </c>
-      <c r="T13" s="1">
         <f t="shared" si="5"/>
         <v>99.431818181818173</v>
       </c>
+      <c r="T13" s="1">
+        <f t="shared" si="6"/>
+        <v>99.431818181818173</v>
+      </c>
       <c r="U13" s="1">
         <v>42.8</v>
       </c>
@@ -1783,10 +1783,10 @@
         <v>60.6</v>
       </c>
       <c r="AA13" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB13" s="1">
-        <f>G13*R13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC13" s="1"/>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1">
         <v>263</v>
@@ -1849,18 +1849,18 @@
       </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="R14" s="5"/>
       <c r="S14" s="1">
-        <f t="shared" si="4"/>
-        <v>38.857142857142854</v>
-      </c>
-      <c r="T14" s="1">
         <f t="shared" si="5"/>
         <v>38.857142857142854</v>
       </c>
+      <c r="T14" s="1">
+        <f t="shared" si="6"/>
+        <v>38.857142857142854</v>
+      </c>
       <c r="U14" s="1">
         <v>15.8</v>
       </c>
@@ -1880,10 +1880,10 @@
         <v>13.2</v>
       </c>
       <c r="AA14" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB14" s="1">
-        <f>G14*R14</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC14" s="1"/>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1">
         <v>46</v>
@@ -1948,18 +1948,18 @@
       </c>
       <c r="P15" s="1"/>
       <c r="Q15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.2</v>
       </c>
       <c r="R15" s="5"/>
       <c r="S15" s="1">
-        <f t="shared" si="4"/>
-        <v>23.064516129032256</v>
-      </c>
-      <c r="T15" s="1">
         <f t="shared" si="5"/>
         <v>23.064516129032256</v>
       </c>
+      <c r="T15" s="1">
+        <f t="shared" si="6"/>
+        <v>23.064516129032256</v>
+      </c>
       <c r="U15" s="1">
         <v>9.1999999999999993</v>
       </c>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="AA15" s="1"/>
       <c r="AB15" s="1">
-        <f>G15*R15</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC15" s="1"/>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1">
         <v>75</v>
@@ -2045,18 +2045,18 @@
       </c>
       <c r="P16" s="1"/>
       <c r="Q16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.6</v>
       </c>
       <c r="R16" s="5"/>
       <c r="S16" s="1">
-        <f t="shared" si="4"/>
-        <v>23.333333333333336</v>
-      </c>
-      <c r="T16" s="1">
         <f t="shared" si="5"/>
         <v>23.333333333333336</v>
       </c>
+      <c r="T16" s="1">
+        <f t="shared" si="6"/>
+        <v>23.333333333333336</v>
+      </c>
       <c r="U16" s="1">
         <v>9.6</v>
       </c>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1">
-        <f>G16*R16</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC16" s="1"/>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="17" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="1">
         <v>389</v>
@@ -2144,19 +2144,19 @@
         <v>200</v>
       </c>
       <c r="Q17" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>63</v>
       </c>
       <c r="R17" s="5">
-        <f t="shared" ref="R7:R44" si="6">20*Q17-P17-O17-F17</f>
+        <f t="shared" ref="R17:R43" si="7">20*Q17-P17-O17-F17</f>
         <v>482</v>
       </c>
       <c r="S17" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="T17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12.34920634920635</v>
       </c>
       <c r="U17" s="1">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1">
-        <f>G17*R17</f>
+        <f t="shared" si="3"/>
         <v>86.759999999999991</v>
       </c>
       <c r="AC17" s="1"/>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="18" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1">
         <v>323</v>
@@ -2242,19 +2242,19 @@
       </c>
       <c r="P18" s="1"/>
       <c r="Q18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>28.4</v>
       </c>
       <c r="R18" s="5">
+        <f t="shared" si="7"/>
+        <v>358</v>
+      </c>
+      <c r="S18" s="1">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="T18" s="1">
         <f t="shared" si="6"/>
-        <v>358</v>
-      </c>
-      <c r="S18" s="1">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="T18" s="1">
-        <f t="shared" si="5"/>
         <v>7.394366197183099</v>
       </c>
       <c r="U18" s="1">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1">
-        <f>G18*R18</f>
+        <f t="shared" si="3"/>
         <v>64.44</v>
       </c>
       <c r="AC18" s="1"/>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="19" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="1">
         <v>43</v>
@@ -2338,18 +2338,18 @@
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
       <c r="R19" s="5"/>
       <c r="S19" s="1">
-        <f t="shared" si="4"/>
-        <v>102.5</v>
-      </c>
-      <c r="T19" s="1">
         <f t="shared" si="5"/>
         <v>102.5</v>
       </c>
+      <c r="T19" s="1">
+        <f t="shared" si="6"/>
+        <v>102.5</v>
+      </c>
       <c r="U19" s="1">
         <v>0.8</v>
       </c>
@@ -2369,10 +2369,10 @@
         <v>3.2</v>
       </c>
       <c r="AA19" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB19" s="1">
-        <f>G19*R19</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC19" s="1"/>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="20" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="1">
         <v>61</v>
@@ -2433,18 +2433,18 @@
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
       <c r="R20" s="5"/>
       <c r="S20" s="1">
-        <f t="shared" si="4"/>
-        <v>71.25</v>
-      </c>
-      <c r="T20" s="1">
         <f t="shared" si="5"/>
         <v>71.25</v>
       </c>
+      <c r="T20" s="1">
+        <f t="shared" si="6"/>
+        <v>71.25</v>
+      </c>
       <c r="U20" s="1">
         <v>1</v>
       </c>
@@ -2464,10 +2464,10 @@
         <v>0.6</v>
       </c>
       <c r="AA20" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB20" s="1">
-        <f>G20*R20</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC20" s="1"/>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="21" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="1">
         <v>170</v>
@@ -2532,18 +2532,18 @@
         <v>78</v>
       </c>
       <c r="Q21" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="R21" s="5"/>
       <c r="S21" s="1">
-        <f t="shared" si="4"/>
-        <v>46.022727272727266</v>
-      </c>
-      <c r="T21" s="1">
         <f t="shared" si="5"/>
         <v>46.022727272727266</v>
       </c>
+      <c r="T21" s="1">
+        <f t="shared" si="6"/>
+        <v>46.022727272727266</v>
+      </c>
       <c r="U21" s="1">
         <v>5.8</v>
       </c>
@@ -2563,10 +2563,10 @@
         <v>3.8</v>
       </c>
       <c r="AA21" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB21" s="1">
-        <f>G21*R21</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC21" s="1"/>
@@ -2592,10 +2592,10 @@
     </row>
     <row r="22" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C22" s="1">
         <v>102</v>
@@ -2633,18 +2633,18 @@
         <v>152</v>
       </c>
       <c r="Q22" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="R22" s="5"/>
       <c r="S22" s="1">
-        <f t="shared" si="4"/>
-        <v>23.428571428571427</v>
-      </c>
-      <c r="T22" s="1">
         <f t="shared" si="5"/>
         <v>23.428571428571427</v>
       </c>
+      <c r="T22" s="1">
+        <f t="shared" si="6"/>
+        <v>23.428571428571427</v>
+      </c>
       <c r="U22" s="1">
         <v>21.4</v>
       </c>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1">
-        <f>G22*R22</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC22" s="1"/>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="23" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
@@ -2726,19 +2726,19 @@
       </c>
       <c r="P23" s="1"/>
       <c r="Q23" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="R23" s="5">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="S23" s="1">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="T23" s="1">
         <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="S23" s="1">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="T23" s="1">
-        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="U23" s="1">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1">
-        <f>G23*R23</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="AC23" s="1"/>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="24" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="1">
         <v>13</v>
@@ -2824,18 +2824,18 @@
       </c>
       <c r="P24" s="1"/>
       <c r="Q24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="R24" s="5"/>
       <c r="S24" s="1">
-        <f t="shared" si="4"/>
-        <v>28.9</v>
-      </c>
-      <c r="T24" s="1">
         <f t="shared" si="5"/>
         <v>28.9</v>
       </c>
+      <c r="T24" s="1">
+        <f t="shared" si="6"/>
+        <v>28.9</v>
+      </c>
       <c r="U24" s="1">
         <v>18.2</v>
       </c>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1">
-        <f>G24*R24</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC24" s="1"/>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="25" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1">
         <v>150</v>
@@ -2921,18 +2921,18 @@
         <v>40</v>
       </c>
       <c r="Q25" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.8</v>
       </c>
       <c r="R25" s="5"/>
       <c r="S25" s="1">
-        <f t="shared" si="4"/>
-        <v>33.707865168539321</v>
-      </c>
-      <c r="T25" s="1">
         <f t="shared" si="5"/>
         <v>33.707865168539321</v>
       </c>
+      <c r="T25" s="1">
+        <f t="shared" si="6"/>
+        <v>33.707865168539321</v>
+      </c>
       <c r="U25" s="1">
         <v>14.6</v>
       </c>
@@ -2952,10 +2952,10 @@
         <v>11.6</v>
       </c>
       <c r="AA25" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB25" s="1">
-        <f>G25*R25</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC25" s="1"/>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="26" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="1">
         <v>52</v>
@@ -3020,18 +3020,18 @@
         <v>50</v>
       </c>
       <c r="Q26" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>37</v>
       </c>
       <c r="R26" s="5"/>
       <c r="S26" s="1">
-        <f t="shared" si="4"/>
-        <v>34.243243243243242</v>
-      </c>
-      <c r="T26" s="1">
         <f t="shared" si="5"/>
         <v>34.243243243243242</v>
       </c>
+      <c r="T26" s="1">
+        <f t="shared" si="6"/>
+        <v>34.243243243243242</v>
+      </c>
       <c r="U26" s="1">
         <v>51.2</v>
       </c>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1">
-        <f>G26*R26</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC26" s="1"/>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="27" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="1">
         <v>474</v>
@@ -3115,18 +3115,18 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.8</v>
       </c>
       <c r="R27" s="5"/>
       <c r="S27" s="1">
-        <f t="shared" si="4"/>
-        <v>214.28571428571431</v>
-      </c>
-      <c r="T27" s="1">
         <f t="shared" si="5"/>
         <v>214.28571428571431</v>
       </c>
+      <c r="T27" s="1">
+        <f t="shared" si="6"/>
+        <v>214.28571428571431</v>
+      </c>
       <c r="U27" s="1">
         <v>6.2</v>
       </c>
@@ -3146,10 +3146,10 @@
         <v>6</v>
       </c>
       <c r="AA27" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB27" s="1">
-        <f>G27*R27</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC27" s="1"/>
@@ -3175,10 +3175,10 @@
     </row>
     <row r="28" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1">
         <v>109</v>
@@ -3214,18 +3214,18 @@
         <v>30</v>
       </c>
       <c r="Q28" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
       <c r="R28" s="5"/>
       <c r="S28" s="1">
-        <f t="shared" si="4"/>
-        <v>355</v>
-      </c>
-      <c r="T28" s="1">
         <f t="shared" si="5"/>
         <v>355</v>
       </c>
+      <c r="T28" s="1">
+        <f t="shared" si="6"/>
+        <v>355</v>
+      </c>
       <c r="U28" s="1">
         <v>3.6</v>
       </c>
@@ -3245,10 +3245,10 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="AA28" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB28" s="1">
-        <f>G28*R28</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC28" s="1"/>
@@ -3274,10 +3274,10 @@
     </row>
     <row r="29" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29" s="1">
         <v>493</v>
@@ -3311,18 +3311,18 @@
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>64.400000000000006</v>
       </c>
       <c r="R29" s="5"/>
       <c r="S29" s="1">
-        <f t="shared" si="4"/>
-        <v>27.62422360248447</v>
-      </c>
-      <c r="T29" s="1">
         <f t="shared" si="5"/>
         <v>27.62422360248447</v>
       </c>
+      <c r="T29" s="1">
+        <f t="shared" si="6"/>
+        <v>27.62422360248447</v>
+      </c>
       <c r="U29" s="1">
         <v>50.2</v>
       </c>
@@ -3342,10 +3342,10 @@
         <v>19.2</v>
       </c>
       <c r="AA29" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB29" s="1">
-        <f>G29*R29</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC29" s="1"/>
@@ -3371,10 +3371,10 @@
     </row>
     <row r="30" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="1">
         <v>418</v>
@@ -3408,18 +3408,18 @@
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>27.6</v>
       </c>
       <c r="R30" s="5"/>
       <c r="S30" s="1">
-        <f t="shared" si="4"/>
-        <v>26.44927536231884</v>
-      </c>
-      <c r="T30" s="1">
         <f t="shared" si="5"/>
         <v>26.44927536231884</v>
       </c>
+      <c r="T30" s="1">
+        <f t="shared" si="6"/>
+        <v>26.44927536231884</v>
+      </c>
       <c r="U30" s="1">
         <v>9</v>
       </c>
@@ -3439,10 +3439,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="AA30" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB30" s="1">
-        <f>G30*R30</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC30" s="1"/>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="31" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="1">
         <v>57</v>
@@ -3507,19 +3507,19 @@
       </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.6</v>
       </c>
       <c r="R31" s="5">
+        <f t="shared" si="7"/>
+        <v>46</v>
+      </c>
+      <c r="S31" s="1">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="T31" s="1">
         <f t="shared" si="6"/>
-        <v>46</v>
-      </c>
-      <c r="S31" s="1">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="T31" s="1">
-        <f t="shared" si="5"/>
         <v>14.651162790697676</v>
       </c>
       <c r="U31" s="1">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1">
-        <f>G31*R31</f>
+        <f t="shared" si="3"/>
         <v>6.44</v>
       </c>
       <c r="AC31" s="1"/>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="32" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="1">
         <v>136</v>
@@ -3607,19 +3607,19 @@
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="R32" s="5">
+        <f t="shared" si="7"/>
+        <v>52</v>
+      </c>
+      <c r="S32" s="1">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="T32" s="1">
         <f t="shared" si="6"/>
-        <v>52</v>
-      </c>
-      <c r="S32" s="1">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="T32" s="1">
-        <f t="shared" si="5"/>
         <v>14.09090909090909</v>
       </c>
       <c r="U32" s="1">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1">
-        <f>G32*R32</f>
+        <f t="shared" si="3"/>
         <v>9.36</v>
       </c>
       <c r="AC32" s="1"/>
@@ -3668,10 +3668,10 @@
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" s="1">
         <v>139.89400000000001</v>
@@ -3701,18 +3701,18 @@
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.67720000000000002</v>
       </c>
       <c r="R33" s="5"/>
       <c r="S33" s="1">
-        <f t="shared" si="4"/>
-        <v>201.57708210277613</v>
-      </c>
-      <c r="T33" s="1">
         <f t="shared" si="5"/>
         <v>201.57708210277613</v>
       </c>
+      <c r="T33" s="1">
+        <f t="shared" si="6"/>
+        <v>201.57708210277613</v>
+      </c>
       <c r="U33" s="1">
         <v>0.67120000000000002</v>
       </c>
@@ -3732,10 +3732,10 @@
         <v>4.3655999999999997</v>
       </c>
       <c r="AA33" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB33" s="1">
-        <f>G33*R33</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC33" s="1"/>
@@ -3761,10 +3761,10 @@
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34" s="1">
         <v>58.366</v>
@@ -3790,18 +3790,18 @@
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R34" s="5"/>
       <c r="S34" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T34" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="T34" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="U34" s="1">
         <v>3.8391999999999999</v>
       </c>
@@ -3821,10 +3821,10 @@
         <v>0</v>
       </c>
       <c r="AA34" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB34" s="1">
-        <f>G34*R34</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC34" s="1"/>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="35" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="1">
         <v>31.417999999999999</v>
@@ -3889,18 +3889,18 @@
         <v>99</v>
       </c>
       <c r="Q35" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.2115999999999998</v>
       </c>
       <c r="R35" s="5"/>
       <c r="S35" s="1">
-        <f t="shared" si="4"/>
-        <v>51.176983435047958</v>
-      </c>
-      <c r="T35" s="1">
         <f t="shared" si="5"/>
         <v>51.176983435047958</v>
       </c>
+      <c r="T35" s="1">
+        <f t="shared" si="6"/>
+        <v>51.176983435047958</v>
+      </c>
       <c r="U35" s="1">
         <v>9.9192</v>
       </c>
@@ -3920,10 +3920,10 @@
         <v>1.8355999999999999</v>
       </c>
       <c r="AA35" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB35" s="1">
-        <f>G35*R35</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC35" s="1"/>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="36" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" s="1">
         <v>156.768</v>
@@ -3982,18 +3982,18 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.61919999999999997</v>
       </c>
       <c r="R36" s="5"/>
       <c r="S36" s="1">
-        <f t="shared" si="4"/>
-        <v>248.17829457364343</v>
-      </c>
-      <c r="T36" s="1">
         <f t="shared" si="5"/>
         <v>248.17829457364343</v>
       </c>
+      <c r="T36" s="1">
+        <f t="shared" si="6"/>
+        <v>248.17829457364343</v>
+      </c>
       <c r="U36" s="1">
         <v>4.4596</v>
       </c>
@@ -4013,10 +4013,10 @@
         <v>0.48559999999999998</v>
       </c>
       <c r="AA36" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB36" s="1">
-        <f>G36*R36</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC36" s="1"/>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="37" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="1">
         <v>329</v>
@@ -4079,7 +4079,7 @@
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>38.6</v>
       </c>
       <c r="R37" s="5">
@@ -4087,11 +4087,11 @@
         <v>553.80000000000007</v>
       </c>
       <c r="S37" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="T37" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.6528497409326421</v>
       </c>
       <c r="U37" s="1">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1">
-        <f>G37*R37</f>
+        <f t="shared" si="3"/>
         <v>55.38000000000001</v>
       </c>
       <c r="AC37" s="1"/>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="38" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C38" s="1">
         <v>439</v>
@@ -4179,19 +4179,19 @@
       </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>31.6</v>
       </c>
       <c r="R38" s="5">
+        <f t="shared" si="7"/>
+        <v>45</v>
+      </c>
+      <c r="S38" s="1">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="T38" s="1">
         <f t="shared" si="6"/>
-        <v>45</v>
-      </c>
-      <c r="S38" s="1">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="T38" s="1">
-        <f t="shared" si="5"/>
         <v>18.575949367088608</v>
       </c>
       <c r="U38" s="1">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1">
-        <f>G38*R38</f>
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
       <c r="AC38" s="1"/>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C39" s="1">
         <v>34.707000000000001</v>
@@ -4269,18 +4269,18 @@
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R39" s="5"/>
       <c r="S39" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T39" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="T39" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="U39" s="1">
         <v>1.3344</v>
       </c>
@@ -4300,10 +4300,10 @@
         <v>0.48</v>
       </c>
       <c r="AA39" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB39" s="1">
-        <f>G39*R39</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC39" s="1"/>
@@ -4329,10 +4329,10 @@
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C40" s="1">
         <v>17</v>
@@ -4368,18 +4368,18 @@
       </c>
       <c r="P40" s="1"/>
       <c r="Q40" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="R40" s="5"/>
       <c r="S40" s="1">
-        <f t="shared" si="4"/>
-        <v>26.413043478260871</v>
-      </c>
-      <c r="T40" s="1">
         <f t="shared" si="5"/>
         <v>26.413043478260871</v>
       </c>
+      <c r="T40" s="1">
+        <f t="shared" si="6"/>
+        <v>26.413043478260871</v>
+      </c>
       <c r="U40" s="1">
         <v>16</v>
       </c>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1">
-        <f>G40*R40</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC40" s="1"/>
@@ -4426,10 +4426,10 @@
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C41" s="1">
         <v>77</v>
@@ -4463,19 +4463,19 @@
         <v>80</v>
       </c>
       <c r="Q41" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="R41" s="5">
+        <f t="shared" si="7"/>
+        <v>38</v>
+      </c>
+      <c r="S41" s="1">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="T41" s="1">
         <f t="shared" si="6"/>
-        <v>38</v>
-      </c>
-      <c r="S41" s="1">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="T41" s="1">
-        <f t="shared" si="5"/>
         <v>16.122448979591837</v>
       </c>
       <c r="U41" s="1">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AA41" s="1"/>
       <c r="AB41" s="1">
-        <f>G41*R41</f>
+        <f t="shared" si="3"/>
         <v>7.6000000000000005</v>
       </c>
       <c r="AC41" s="1"/>
@@ -4524,10 +4524,10 @@
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C42" s="1">
         <v>19.059999999999999</v>
@@ -4563,18 +4563,18 @@
         <v>45</v>
       </c>
       <c r="Q42" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.5568</v>
       </c>
       <c r="R42" s="5"/>
       <c r="S42" s="1">
-        <f t="shared" si="4"/>
-        <v>37.654881101376724</v>
-      </c>
-      <c r="T42" s="1">
         <f t="shared" si="5"/>
         <v>37.654881101376724</v>
       </c>
+      <c r="T42" s="1">
+        <f t="shared" si="6"/>
+        <v>37.654881101376724</v>
+      </c>
       <c r="U42" s="1">
         <v>5.3572000000000006</v>
       </c>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1">
-        <f>G42*R42</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC42" s="1"/>
@@ -4621,10 +4621,10 @@
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C43" s="1">
         <v>93</v>
@@ -4656,19 +4656,19 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="R43" s="5">
+        <f t="shared" si="7"/>
+        <v>117</v>
+      </c>
+      <c r="S43" s="1">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="T43" s="1">
         <f t="shared" si="6"/>
-        <v>117</v>
-      </c>
-      <c r="S43" s="1">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="T43" s="1">
-        <f t="shared" si="5"/>
         <v>10.25</v>
       </c>
       <c r="U43" s="1">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1">
-        <f>G43*R43</f>
+        <f t="shared" si="3"/>
         <v>23.400000000000002</v>
       </c>
       <c r="AC43" s="1"/>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="44" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
@@ -4750,18 +4750,18 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.1175999999999999</v>
       </c>
       <c r="R44" s="5"/>
       <c r="S44" s="1">
-        <f t="shared" si="4"/>
-        <v>48.151208915753685</v>
-      </c>
-      <c r="T44" s="1">
         <f t="shared" si="5"/>
         <v>48.151208915753685</v>
       </c>
+      <c r="T44" s="1">
+        <f t="shared" si="6"/>
+        <v>48.151208915753685</v>
+      </c>
       <c r="U44" s="1">
         <v>0</v>
       </c>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1">
-        <f>G44*R44</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AC44" s="1"/>
